--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,135 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127361503</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56587</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lunden, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>283312</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6540377</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oskar Kindvall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Kindvall, Malin Strand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>127361503</v>
       </c>
       <c r="B5" t="n">
-        <v>56587</v>
+        <v>56591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>127361503</v>
       </c>
       <c r="B5" t="n">
-        <v>56591</v>
+        <v>56593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>127361503</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>127361503</v>
       </c>
       <c r="B5" t="n">
-        <v>56596</v>
+        <v>56602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59406-2024 artfynd.xlsx
+++ b/artfynd/A 59406-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111323536</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,6 +949,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101884921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1076,6 +1091,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110502320</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1205,6 +1225,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111186175</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1343,6 +1368,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116551116</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1476,6 +1506,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361143</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1605,6 +1640,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1734,6 +1774,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1859,6 +1904,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361088</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1993,8 +2043,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>